--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -10,8 +10,9 @@
     <sheet name="per_image" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="width" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="per_lacuna" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="biological_limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="per_lacuna" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,11 +447,6 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>n_bridges</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,9 +468,6 @@
       <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="n">
-        <v>24</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4078</v>
+        <v>4.504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -735,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>396.75</v>
+        <v>422.875</v>
       </c>
       <c r="D13" t="n">
-        <v>356.5</v>
+        <v>368.5</v>
       </c>
       <c r="E13" t="n">
-        <v>128.3319</v>
+        <v>133.1749</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -764,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>982</v>
+        <v>1024.375</v>
       </c>
       <c r="D14" t="n">
-        <v>914</v>
+        <v>889</v>
       </c>
       <c r="E14" t="n">
-        <v>329.7241</v>
+        <v>346.6117</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -793,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1860.5611</v>
+        <v>2735.3376</v>
       </c>
       <c r="D15" t="n">
-        <v>997.753</v>
+        <v>1863.4266</v>
       </c>
       <c r="E15" t="n">
-        <v>1996.4827</v>
+        <v>2088.9615</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -822,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>125.625</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="E16" t="n">
-        <v>85.157</v>
+        <v>102.2154</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -851,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.4567</v>
+        <v>22.5629</v>
       </c>
       <c r="D17" t="n">
-        <v>25.0725</v>
+        <v>22.6394</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7151</v>
+        <v>2.7001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1025,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03800643</v>
+        <v>0.04052149</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03766433</v>
+        <v>0.03908006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00650669</v>
+        <v>0.00643539</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1054,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04004776</v>
+        <v>0.0416417</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04065321</v>
+        <v>0.04159772</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008509630000000001</v>
+        <v>0.00786325</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1083,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.538</v>
+        <v>3.7643</v>
       </c>
       <c r="D25" t="n">
-        <v>3.6845</v>
+        <v>3.936</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6393</v>
+        <v>0.6189</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1112,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>317.125</v>
+        <v>351.625</v>
       </c>
       <c r="D26" t="n">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E26" t="n">
-        <v>135.0423</v>
+        <v>139.5881</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1141,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>673.25</v>
+        <v>809.5</v>
       </c>
       <c r="D27" t="n">
-        <v>584.5</v>
+        <v>668.5</v>
       </c>
       <c r="E27" t="n">
-        <v>354.146</v>
+        <v>395.5192</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1170,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>445.9204</v>
+        <v>477.0898</v>
       </c>
       <c r="D28" t="n">
-        <v>397.3686</v>
+        <v>412.6051</v>
       </c>
       <c r="E28" t="n">
-        <v>141.6018</v>
+        <v>144.0379</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1199,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1103.9582</v>
+        <v>1157.942</v>
       </c>
       <c r="D29" t="n">
-        <v>1012.9884</v>
+        <v>991.5890000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>365.4032</v>
+        <v>380.6931</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1228,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.75</v>
+        <v>10.875</v>
       </c>
       <c r="D30" t="n">
         <v>9.5</v>
       </c>
       <c r="E30" t="n">
-        <v>5.0356</v>
+        <v>5.0832</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1257,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
         <v>12.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.4641</v>
+        <v>4.0356</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1286,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>5.1547</v>
+        <v>5.3452</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1315,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.5385</v>
+        <v>6.2246</v>
       </c>
       <c r="D33" t="n">
-        <v>5.518</v>
+        <v>6.2912</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3651</v>
+        <v>0.4579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1400,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35267</v>
+        <v>32768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1420,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03464652</v>
+        <v>0.03219148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1440,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00047155</v>
+        <v>0.00066018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1520,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>720</v>
+        <v>309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>48.9819</v>
+        <v>106.0453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1580,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03869506</v>
+        <v>0.03621496</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1600,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03502703</v>
+        <v>0.03353699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1673,7 +1666,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.7755</v>
+        <v>6.7319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1693,7 +1686,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1713,7 +1706,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1753,7 +1746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32998</v>
+        <v>31623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1772,1184 +1765,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lacuna_id</t>
+          <t>block</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>area_px2</t>
+          <t>item</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>major_axis_length_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>minor_axis_length_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>aspect_ratio</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eccentricity</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>solidity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>orientation_rad</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroid_row_px</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>centroid_col_px</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>on_border</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roots_count</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ring_length_r30_px</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ring_length_r60_px</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>owned_length_px</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>edge_count</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>mean_edge_length_px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>perimeter_px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ring_area_r30_px2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>ring_area_r60_px2</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r30</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>in_frame_fraction_r60</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ring_density_r30</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ring_density_r60</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>roots_per_100px_perimeter</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r30_px</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ring_attached_length_r60_px</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r30_px</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>ring_length_w_r60_px</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r10</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r20</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>sholl_crossings_r30</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>ring_width_mean_r30_px</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>report only, nothing is pruned or filtered by this block</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>along the network from the owning lacuna's surface to a thread end</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>range_um</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[25.0, 50.0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>range_px_applied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[192, 385]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>range_um_applied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[24.96, 50.05]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>n_threads</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>17.5478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>42.2537</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>max_um</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>50.0471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fraction_in_range</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3295</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fraction_below_range</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6705</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>thread_length</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fraction_above_range</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>threads leaving the lacuna surface, interior lacunae only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>n_lacunae</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>roots_per_lacuna</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2 x the distance transform of the mask at each sampled skeleton pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>is_an_upper_bound</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>9321</v>
-      </c>
-      <c r="C2" t="n">
-        <v>210.577</v>
-      </c>
-      <c r="D2" t="n">
-        <v>69.70659999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.0209</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9436</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.3112</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31.8256</v>
-      </c>
-      <c r="J2" t="n">
-        <v>428.1616</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" t="n">
-        <v>368</v>
-      </c>
-      <c r="N2" t="n">
-        <v>955</v>
-      </c>
-      <c r="O2" t="n">
-        <v>480.7056</v>
-      </c>
-      <c r="P2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>22.8907</v>
-      </c>
-      <c r="R2" t="n">
-        <v>769.5412</v>
-      </c>
-      <c r="S2" t="n">
-        <v>14367</v>
-      </c>
-      <c r="T2" t="n">
-        <v>29344</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.6579</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.6229</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.02561425</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.03254498</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.2995</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>254</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>366</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>398.7056</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1026.4113</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6.2657</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2563</v>
-      </c>
-      <c r="C3" t="n">
-        <v>90.1026</v>
-      </c>
-      <c r="D3" t="n">
-        <v>36.7546</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.4515</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9144</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.5381</v>
-      </c>
-      <c r="I3" t="n">
-        <v>342.6867</v>
-      </c>
-      <c r="J3" t="n">
-        <v>87.595</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M3" t="n">
-        <v>372</v>
-      </c>
-      <c r="N3" t="n">
-        <v>992</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1236.1463</v>
-      </c>
-      <c r="P3" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>23.3235</v>
-      </c>
-      <c r="R3" t="n">
-        <v>234.8944</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9374</v>
-      </c>
-      <c r="T3" t="n">
-        <v>20769</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.9593</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.03968423</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.04776349</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.2572</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>303</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>656</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>421.7767</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1099.5361</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.0017</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3496</v>
-      </c>
-      <c r="C4" t="n">
-        <v>113.8955</v>
-      </c>
-      <c r="D4" t="n">
-        <v>40.712</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.7976</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9339</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8552</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1.2503</v>
-      </c>
-      <c r="I4" t="n">
-        <v>434.2543</v>
-      </c>
-      <c r="J4" t="n">
-        <v>701.9173</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13</v>
-      </c>
-      <c r="M4" t="n">
-        <v>373</v>
-      </c>
-      <c r="N4" t="n">
-        <v>988</v>
-      </c>
-      <c r="O4" t="n">
-        <v>966.3768</v>
-      </c>
-      <c r="P4" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>31.1734</v>
-      </c>
-      <c r="R4" t="n">
-        <v>313.9483</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11274</v>
-      </c>
-      <c r="T4" t="n">
-        <v>26474</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.03308497</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.03731963</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4.1408</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>312</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>591</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>420.3747</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1118.0874</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.2647</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4123</v>
-      </c>
-      <c r="C5" t="n">
-        <v>159.7514</v>
-      </c>
-      <c r="D5" t="n">
-        <v>36.5648</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.369</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9735</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7865</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.4743</v>
-      </c>
-      <c r="I5" t="n">
-        <v>433.9658</v>
-      </c>
-      <c r="J5" t="n">
-        <v>210.1004</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18</v>
-      </c>
-      <c r="M5" t="n">
-        <v>652</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1616</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6469.8006</v>
-      </c>
-      <c r="P5" t="n">
-        <v>277</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>23.3567</v>
-      </c>
-      <c r="R5" t="n">
-        <v>456.9605</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14983</v>
-      </c>
-      <c r="T5" t="n">
-        <v>32605</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.04351598</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.04956295</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.9391</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>622</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1480</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>726.1858999999999</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1818.1778</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.9855</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1521</v>
-      </c>
-      <c r="C6" t="n">
-        <v>89.60899999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>30.1271</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.9744</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9418</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.2077</v>
-      </c>
-      <c r="I6" t="n">
-        <v>520.501</v>
-      </c>
-      <c r="J6" t="n">
-        <v>556.9512999999999</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" t="n">
-        <v>328</v>
-      </c>
-      <c r="N6" t="n">
-        <v>683</v>
-      </c>
-      <c r="O6" t="n">
-        <v>546.4163</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>23.7572</v>
-      </c>
-      <c r="R6" t="n">
-        <v>233.2376</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9202</v>
-      </c>
-      <c r="T6" t="n">
-        <v>19621</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.03564443</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.03480964</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>227</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>393</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>374.3625</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>776.7666</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.7484</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>862</v>
-      </c>
-      <c r="C7" t="n">
-        <v>61.0771</v>
-      </c>
-      <c r="D7" t="n">
-        <v>21.2942</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.8683</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9373</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.7077</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.4443</v>
-      </c>
-      <c r="I7" t="n">
-        <v>545.4838</v>
-      </c>
-      <c r="J7" t="n">
-        <v>438.1636</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>341</v>
-      </c>
-      <c r="N7" t="n">
-        <v>840</v>
-      </c>
-      <c r="O7" t="n">
-        <v>940.0265000000001</v>
-      </c>
-      <c r="P7" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>16.7862</v>
-      </c>
-      <c r="R7" t="n">
-        <v>166.1249</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7387</v>
-      </c>
-      <c r="T7" t="n">
-        <v>17424</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.04616218</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.04820937</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.0098</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>265</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>578</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>373.5219</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>926.4407</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.1878</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>547</v>
-      </c>
-      <c r="C8" t="n">
-        <v>50.4784</v>
-      </c>
-      <c r="D8" t="n">
-        <v>17.0874</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.9541</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8116</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.4973</v>
-      </c>
-      <c r="I8" t="n">
-        <v>672.9872</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1013.4461</v>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>150</v>
-      </c>
-      <c r="N8" t="n">
-        <v>415</v>
-      </c>
-      <c r="O8" t="n">
-        <v>294.1198</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>36.765</v>
-      </c>
-      <c r="R8" t="n">
-        <v>122.6041</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3917</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10590</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.6212</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.5802</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03829461</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.03918791</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.4469</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>194</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>170.9239</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>478.6295</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.3724</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3601</v>
-      </c>
-      <c r="C9" t="n">
-        <v>127.9756</v>
-      </c>
-      <c r="D9" t="n">
-        <v>37.0473</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.4544</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9572000000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8909</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.4857</v>
-      </c>
-      <c r="I9" t="n">
-        <v>713.9261</v>
-      </c>
-      <c r="J9" t="n">
-        <v>152.0064</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>13</v>
-      </c>
-      <c r="M9" t="n">
-        <v>526</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1305</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2897.3708</v>
-      </c>
-      <c r="P9" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>28.1298</v>
-      </c>
-      <c r="R9" t="n">
-        <v>329.5219</v>
-      </c>
-      <c r="S9" t="n">
-        <v>12020</v>
-      </c>
-      <c r="T9" t="n">
-        <v>29668</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.0437604</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.04398679</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.9451</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>375</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>815</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>589.9016</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1448.7443</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.7045</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1853</v>
-      </c>
-      <c r="C10" t="n">
-        <v>92.0913</v>
-      </c>
-      <c r="D10" t="n">
-        <v>27.1748</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.3889</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.9555</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9155</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.2655</v>
-      </c>
-      <c r="I10" t="n">
-        <v>723.7311999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>828.8516</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>323</v>
-      </c>
-      <c r="N10" t="n">
-        <v>758</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1029.1291</v>
-      </c>
-      <c r="P10" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>26.3879</v>
-      </c>
-      <c r="R10" t="n">
-        <v>222.7523</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9104</v>
-      </c>
-      <c r="T10" t="n">
-        <v>23858</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.03547891</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.03177131</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.1425</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>221</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>447</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>368.6468</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>884.46</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.3314</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2780</v>
-      </c>
-      <c r="C11" t="n">
-        <v>93.6835</v>
-      </c>
-      <c r="D11" t="n">
-        <v>39.1668</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.3919</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9084</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.1692</v>
-      </c>
-      <c r="I11" t="n">
-        <v>908.6133</v>
-      </c>
-      <c r="J11" t="n">
-        <v>727.0924</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" t="n">
-        <v>259</v>
-      </c>
-      <c r="N11" t="n">
-        <v>674</v>
-      </c>
-      <c r="O11" t="n">
-        <v>799.2224</v>
-      </c>
-      <c r="P11" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>30.7393</v>
-      </c>
-      <c r="R11" t="n">
-        <v>245.9655</v>
-      </c>
-      <c r="S11" t="n">
-        <v>9693</v>
-      </c>
-      <c r="T11" t="n">
-        <v>25001</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.02672031</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.02695892</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.4394</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>212</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>426</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>292.5929</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>759.4529</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>5.0843</v>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>it includes the optical blur, which widens a thread beyond its true size, and no point spread function is subtracted: the numerical aperture, the emission wavelength and the pinhole are unknown. It is an apparent width in the image, not a canalicular diameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>median_um</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>p10_um</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>apparent_width</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>p90_um</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2963,6 +2179,1197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lacuna_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>area_px2</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>major_axis_length_px</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minor_axis_length_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aspect_ratio</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eccentricity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>solidity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>orientation_rad</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>centroid_row_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>centroid_col_px</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>on_border</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>roots_count</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring_length_r30_px</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_length_r60_px</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>owned_length_px</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mean_edge_length_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ring_width_mean_r30_px</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>9321</v>
+      </c>
+      <c r="C2" t="n">
+        <v>210.577</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69.70659999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.0209</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9436</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.3112</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.8256</v>
+      </c>
+      <c r="J2" t="n">
+        <v>428.1616</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>391</v>
+      </c>
+      <c r="N2" t="n">
+        <v>939</v>
+      </c>
+      <c r="O2" t="n">
+        <v>950.6711</v>
+      </c>
+      <c r="P2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>21.126</v>
+      </c>
+      <c r="R2" t="n">
+        <v>769.5412</v>
+      </c>
+      <c r="S2" t="n">
+        <v>14367</v>
+      </c>
+      <c r="T2" t="n">
+        <v>29344</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.02721515</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.03199973</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.5594</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>313</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>666</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>432.5341</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1020.6417</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>7.3833</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2563</v>
+      </c>
+      <c r="C3" t="n">
+        <v>90.1026</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36.7546</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.4515</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5381</v>
+      </c>
+      <c r="I3" t="n">
+        <v>342.6867</v>
+      </c>
+      <c r="J3" t="n">
+        <v>87.595</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>369</v>
+      </c>
+      <c r="N3" t="n">
+        <v>912</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1039.4234</v>
+      </c>
+      <c r="P3" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.6547</v>
+      </c>
+      <c r="R3" t="n">
+        <v>234.8944</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9374</v>
+      </c>
+      <c r="T3" t="n">
+        <v>20769</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.0393642</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0439116</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.8315</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>323</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>727</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>415.8061</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1019.7666</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6.4993</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3496</v>
+      </c>
+      <c r="C4" t="n">
+        <v>113.8955</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40.712</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.7976</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9339</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8552</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.2503</v>
+      </c>
+      <c r="I4" t="n">
+        <v>434.2543</v>
+      </c>
+      <c r="J4" t="n">
+        <v>701.9173</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" t="n">
+        <v>418</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1040</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1410.6266</v>
+      </c>
+      <c r="P4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25.1898</v>
+      </c>
+      <c r="R4" t="n">
+        <v>313.9483</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11274</v>
+      </c>
+      <c r="T4" t="n">
+        <v>26474</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.03707646</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03928383</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.1408</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>393</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>736</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>475.6173</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1185.9159</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6.3984</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4123</v>
+      </c>
+      <c r="C5" t="n">
+        <v>159.7514</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36.5648</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.369</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7865</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.4743</v>
+      </c>
+      <c r="I5" t="n">
+        <v>433.9658</v>
+      </c>
+      <c r="J5" t="n">
+        <v>210.1004</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" t="n">
+        <v>694</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1734</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6115.3447</v>
+      </c>
+      <c r="P5" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>19.2913</v>
+      </c>
+      <c r="R5" t="n">
+        <v>456.9605</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14983</v>
+      </c>
+      <c r="T5" t="n">
+        <v>32605</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.04631916</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.05318203</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.3767</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>631</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>763.4579</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1946.521</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>7.0022</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1521</v>
+      </c>
+      <c r="C6" t="n">
+        <v>89.60899999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.1271</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.9744</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.2077</v>
+      </c>
+      <c r="I6" t="n">
+        <v>520.501</v>
+      </c>
+      <c r="J6" t="n">
+        <v>556.9512999999999</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>357</v>
+      </c>
+      <c r="N6" t="n">
+        <v>753</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2181.2804</v>
+      </c>
+      <c r="P6" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>24.5088</v>
+      </c>
+      <c r="R6" t="n">
+        <v>233.2376</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19621</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03879591</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.03837725</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>552</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>409.4041</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>869.193</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.184</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>862</v>
+      </c>
+      <c r="C7" t="n">
+        <v>61.0771</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21.2942</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.8683</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9373</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.4443</v>
+      </c>
+      <c r="I7" t="n">
+        <v>545.4838</v>
+      </c>
+      <c r="J7" t="n">
+        <v>438.1636</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>368</v>
+      </c>
+      <c r="N7" t="n">
+        <v>866</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1973.1951</v>
+      </c>
+      <c r="P7" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>18.973</v>
+      </c>
+      <c r="R7" t="n">
+        <v>166.1249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7387</v>
+      </c>
+      <c r="T7" t="n">
+        <v>17424</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.04981725</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04970156</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.2137</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>287</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>610</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>405.4214</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>963.4113</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.5994</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>547</v>
+      </c>
+      <c r="C8" t="n">
+        <v>50.4784</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17.0874</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.9541</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8116</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.4973</v>
+      </c>
+      <c r="I8" t="n">
+        <v>672.9872</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1013.4461</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>130</v>
+      </c>
+      <c r="N8" t="n">
+        <v>379</v>
+      </c>
+      <c r="O8" t="n">
+        <v>261.3625</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>37.3375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>122.6041</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3917</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10590</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.03318866</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.03578848</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.4469</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>153.9239</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>450.529</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.269</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3601</v>
+      </c>
+      <c r="C9" t="n">
+        <v>127.9756</v>
+      </c>
+      <c r="D9" t="n">
+        <v>37.0473</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.4544</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.4857</v>
+      </c>
+      <c r="I9" t="n">
+        <v>713.9261</v>
+      </c>
+      <c r="J9" t="n">
+        <v>152.0064</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" t="n">
+        <v>547</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1341</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6024.1193</v>
+      </c>
+      <c r="P9" t="n">
+        <v>255</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>23.624</v>
+      </c>
+      <c r="R9" t="n">
+        <v>329.5219</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12020</v>
+      </c>
+      <c r="T9" t="n">
+        <v>29668</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04550749</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.04520022</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.6416</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>462</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1138</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>622.4579</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1490.188</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.4083</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1853</v>
+      </c>
+      <c r="C10" t="n">
+        <v>92.0913</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.1748</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.3889</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9155</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.2655</v>
+      </c>
+      <c r="I10" t="n">
+        <v>723.7311999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>828.8516</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>344</v>
+      </c>
+      <c r="N10" t="n">
+        <v>793</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1753.6581</v>
+      </c>
+      <c r="P10" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>21.1284</v>
+      </c>
+      <c r="R10" t="n">
+        <v>222.7523</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9104</v>
+      </c>
+      <c r="T10" t="n">
+        <v>23858</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.03778559</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.03323833</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.0404</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>259</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>594</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>395.8183</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>926.7320999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.0175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2780</v>
+      </c>
+      <c r="C11" t="n">
+        <v>93.6835</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.1668</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.3919</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9084</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1.1692</v>
+      </c>
+      <c r="I11" t="n">
+        <v>908.6133</v>
+      </c>
+      <c r="J11" t="n">
+        <v>727.0924</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>286</v>
+      </c>
+      <c r="N11" t="n">
+        <v>756</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1385.053</v>
+      </c>
+      <c r="P11" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>26.1331</v>
+      </c>
+      <c r="R11" t="n">
+        <v>245.9655</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9693</v>
+      </c>
+      <c r="T11" t="n">
+        <v>25001</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.02950583</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.03023879</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.4394</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>209</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>469</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>328.7351</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>861.8082000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.6877</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2983,7 +3390,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.5</v>
+        <v>8.875</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>4.504</v>
+        <v>3.5632</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>422.875</v>
+        <v>460</v>
       </c>
       <c r="D13" t="n">
-        <v>368.5</v>
+        <v>400.5</v>
       </c>
       <c r="E13" t="n">
-        <v>133.1749</v>
+        <v>143.7856</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1024.375</v>
+        <v>1083.375</v>
       </c>
       <c r="D14" t="n">
-        <v>889</v>
+        <v>939.5</v>
       </c>
       <c r="E14" t="n">
-        <v>346.6117</v>
+        <v>361.3218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2735.3376</v>
+        <v>2933.1362</v>
       </c>
       <c r="D15" t="n">
-        <v>1863.4266</v>
+        <v>1646.0321</v>
       </c>
       <c r="E15" t="n">
-        <v>2088.9615</v>
+        <v>2286.2961</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>125.625</v>
+        <v>138.125</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>102.2154</v>
+        <v>105.0842</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5629</v>
+        <v>21.3005</v>
       </c>
       <c r="D17" t="n">
-        <v>22.6394</v>
+        <v>21.6347</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7001</v>
+        <v>1.7632</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04052149</v>
+        <v>0.0440793</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03908006</v>
+        <v>0.04195089</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00643539</v>
+        <v>0.0069352</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0416417</v>
+        <v>0.04405889</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04159772</v>
+        <v>0.04366502</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00786325</v>
+        <v>0.008148549999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.7643</v>
+        <v>3.2531</v>
       </c>
       <c r="D25" t="n">
-        <v>3.936</v>
+        <v>3.1586</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6189</v>
+        <v>0.9129</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>351.625</v>
+        <v>397.75</v>
       </c>
       <c r="D26" t="n">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="E26" t="n">
-        <v>139.5881</v>
+        <v>138.6916</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>809.5</v>
+        <v>902.875</v>
       </c>
       <c r="D27" t="n">
-        <v>668.5</v>
+        <v>769</v>
       </c>
       <c r="E27" t="n">
-        <v>395.5192</v>
+        <v>392.2617</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>477.0898</v>
+        <v>520.8569</v>
       </c>
       <c r="D28" t="n">
-        <v>412.6051</v>
+        <v>452.8123</v>
       </c>
       <c r="E28" t="n">
-        <v>144.0379</v>
+        <v>155.3532</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1157.942</v>
+        <v>1226.0753</v>
       </c>
       <c r="D29" t="n">
-        <v>991.5890000000001</v>
+        <v>1049.9026</v>
       </c>
       <c r="E29" t="n">
-        <v>380.6931</v>
+        <v>394.1536</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>9.5</v>
       </c>
       <c r="E30" t="n">
-        <v>5.0832</v>
+        <v>3.9799</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.0356</v>
+        <v>3.7033</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3452</v>
+        <v>5.3117</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.2246</v>
+        <v>7.1884</v>
       </c>
       <c r="D33" t="n">
-        <v>6.2912</v>
+        <v>7.3449</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4579</v>
+        <v>0.4664</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32768</v>
+        <v>35082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03219148</v>
+        <v>0.03446477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>672</v>
+        <v>791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00066018</v>
+        <v>0.00077708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>106.0453</v>
+        <v>125.7419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03621496</v>
+        <v>0.03880481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03353699</v>
+        <v>0.03544169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>57</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03446477</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03545798</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.7319</v>
+        <v>7.5376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31623</v>
+        <v>33419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>525</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.5478</v>
+        <v>18.8116</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.39</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42.2537</v>
+        <v>43.7141</v>
       </c>
     </row>
     <row r="12">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3295</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6705</v>
+        <v>0.6173999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2384,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="N2" t="n">
-        <v>939</v>
+        <v>1050</v>
       </c>
       <c r="O2" t="n">
-        <v>950.6711</v>
+        <v>4607.841</v>
       </c>
       <c r="P2" t="n">
-        <v>45</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.126</v>
+        <v>19.6916</v>
       </c>
       <c r="R2" t="n">
         <v>769.5412</v>
@@ -2417,37 +2497,37 @@
         <v>0.6229</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02721515</v>
+        <v>0.02805039</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03199973</v>
+        <v>0.03578244</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5594</v>
+        <v>1.2995</v>
       </c>
       <c r="Z2" t="n">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="AA2" t="n">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="AB2" t="n">
-        <v>432.5341</v>
+        <v>444.3625</v>
       </c>
       <c r="AC2" t="n">
-        <v>1020.6417</v>
+        <v>1138.6833</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
       </c>
       <c r="AE2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF2" t="n">
         <v>12</v>
       </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
       <c r="AG2" t="n">
-        <v>7.3833</v>
+        <v>5.308</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="N3" t="n">
-        <v>912</v>
+        <v>961</v>
       </c>
       <c r="O3" t="n">
-        <v>1039.4234</v>
+        <v>1407.3595</v>
       </c>
       <c r="P3" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.6547</v>
+        <v>19.5467</v>
       </c>
       <c r="R3" t="n">
         <v>234.8944</v>
@@ -2518,37 +2598,37 @@
         <v>0.9593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0393642</v>
+        <v>0.0403243</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0439116</v>
+        <v>0.04627088</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.8315</v>
+        <v>2.5543</v>
       </c>
       <c r="Z3" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AA3" t="n">
-        <v>727</v>
+        <v>853</v>
       </c>
       <c r="AB3" t="n">
-        <v>415.8061</v>
+        <v>425.8772</v>
       </c>
       <c r="AC3" t="n">
-        <v>1019.7666</v>
+        <v>1072.3524</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>11</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.4993</v>
+        <v>7.5912</v>
       </c>
     </row>
     <row r="4">
@@ -2589,19 +2669,19 @@
         <v>13</v>
       </c>
       <c r="M4" t="n">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="N4" t="n">
-        <v>1040</v>
+        <v>1087</v>
       </c>
       <c r="O4" t="n">
-        <v>1410.6266</v>
+        <v>3571.2258</v>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>163</v>
       </c>
       <c r="Q4" t="n">
-        <v>25.1898</v>
+        <v>21.9094</v>
       </c>
       <c r="R4" t="n">
         <v>313.9483</v>
@@ -2619,37 +2699,37 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03707646</v>
+        <v>0.04018095</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03928383</v>
+        <v>0.04105915</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1408</v>
       </c>
       <c r="Z4" t="n">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="AA4" t="n">
-        <v>736</v>
+        <v>883</v>
       </c>
       <c r="AB4" t="n">
-        <v>475.6173</v>
+        <v>519.1737000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1185.9159</v>
+        <v>1247.7149</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.3984</v>
+        <v>7.4864</v>
       </c>
     </row>
     <row r="5">
@@ -2687,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>694</v>
+        <v>743</v>
       </c>
       <c r="N5" t="n">
-        <v>1734</v>
+        <v>1814</v>
       </c>
       <c r="O5" t="n">
-        <v>6115.3447</v>
+        <v>5105.9802</v>
       </c>
       <c r="P5" t="n">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.2913</v>
+        <v>19.4144</v>
       </c>
       <c r="R5" t="n">
         <v>456.9605</v>
@@ -2720,37 +2800,37 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04631916</v>
+        <v>0.04958953</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05318203</v>
+        <v>0.05563564</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.3767</v>
+        <v>3.2826</v>
       </c>
       <c r="Z5" t="n">
-        <v>631</v>
+        <v>671</v>
       </c>
       <c r="AA5" t="n">
-        <v>1650</v>
+        <v>1721</v>
       </c>
       <c r="AB5" t="n">
-        <v>763.4579</v>
+        <v>822.9138</v>
       </c>
       <c r="AC5" t="n">
-        <v>1946.521</v>
+        <v>2034.8347</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.0022</v>
+        <v>7.6399</v>
       </c>
     </row>
     <row r="6">
@@ -2788,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="N6" t="n">
-        <v>753</v>
+        <v>801</v>
       </c>
       <c r="O6" t="n">
-        <v>2181.2804</v>
+        <v>1580.6387</v>
       </c>
       <c r="P6" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.5088</v>
+        <v>21.36</v>
       </c>
       <c r="R6" t="n">
         <v>233.2376</v>
@@ -2821,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03879591</v>
+        <v>0.04357748</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03837725</v>
+        <v>0.04082361</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.43</v>
+        <v>2.5725</v>
       </c>
       <c r="Z6" t="n">
-        <v>249</v>
+        <v>350</v>
       </c>
       <c r="AA6" t="n">
-        <v>552</v>
+        <v>685</v>
       </c>
       <c r="AB6" t="n">
-        <v>409.4041</v>
+        <v>465.3747</v>
       </c>
       <c r="AC6" t="n">
-        <v>869.193</v>
+        <v>930.9209</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.184</v>
+        <v>6.8902</v>
       </c>
     </row>
     <row r="7">
@@ -2889,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="N7" t="n">
-        <v>866</v>
+        <v>918</v>
       </c>
       <c r="O7" t="n">
-        <v>1973.1951</v>
+        <v>1711.4255</v>
       </c>
       <c r="P7" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.973</v>
+        <v>19.0158</v>
       </c>
       <c r="R7" t="n">
         <v>166.1249</v>
@@ -2922,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04981725</v>
+        <v>0.05414918</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04970156</v>
+        <v>0.05268595</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2137</v>
+        <v>4.8157</v>
       </c>
       <c r="Z7" t="n">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="AA7" t="n">
-        <v>610</v>
+        <v>667</v>
       </c>
       <c r="AB7" t="n">
-        <v>405.4214</v>
+        <v>440.2498</v>
       </c>
       <c r="AC7" t="n">
-        <v>963.4113</v>
+        <v>1027.4529</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -2952,7 +3032,7 @@
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.5994</v>
+        <v>6.4357</v>
       </c>
     </row>
     <row r="8">
@@ -2993,19 +3073,19 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="N8" t="n">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="O8" t="n">
-        <v>261.3625</v>
+        <v>405.0437</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.3375</v>
+        <v>33.7536</v>
       </c>
       <c r="R8" t="n">
         <v>122.6041</v>
@@ -3023,25 +3103,25 @@
         <v>0.5802</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03318866</v>
+        <v>0.03676283</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03578848</v>
+        <v>0.03796034</v>
       </c>
       <c r="Y8" t="n">
         <v>2.4469</v>
       </c>
       <c r="Z8" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AA8" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="AB8" t="n">
-        <v>153.9239</v>
+        <v>170.1665</v>
       </c>
       <c r="AC8" t="n">
-        <v>450.529</v>
+        <v>477.4285</v>
       </c>
       <c r="AD8" t="n">
         <v>3</v>
@@ -3053,7 +3133,7 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.269</v>
+        <v>6.0372</v>
       </c>
     </row>
     <row r="9">
@@ -3091,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>547</v>
+        <v>614</v>
       </c>
       <c r="N9" t="n">
-        <v>1341</v>
+        <v>1436</v>
       </c>
       <c r="O9" t="n">
-        <v>6024.1193</v>
+        <v>7460.3662</v>
       </c>
       <c r="P9" t="n">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.624</v>
+        <v>22.6072</v>
       </c>
       <c r="R9" t="n">
         <v>329.5219</v>
@@ -3124,37 +3204,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.04550749</v>
+        <v>0.05108153</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04520022</v>
+        <v>0.04840232</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.6416</v>
+        <v>3.0347</v>
       </c>
       <c r="Z9" t="n">
-        <v>462</v>
+        <v>525</v>
       </c>
       <c r="AA9" t="n">
-        <v>1138</v>
+        <v>1225</v>
       </c>
       <c r="AB9" t="n">
-        <v>622.4579</v>
+        <v>691.7006</v>
       </c>
       <c r="AC9" t="n">
-        <v>1490.188</v>
+        <v>1590.0164</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.4083</v>
+        <v>7.5804</v>
       </c>
     </row>
     <row r="10">
@@ -3192,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="N10" t="n">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="O10" t="n">
-        <v>1753.6581</v>
+        <v>1122.857</v>
       </c>
       <c r="P10" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.1284</v>
+        <v>23.3929</v>
       </c>
       <c r="R10" t="n">
         <v>222.7523</v>
@@ -3225,28 +3305,28 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03778559</v>
+        <v>0.04020211</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03323833</v>
+        <v>0.03491491</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.0404</v>
+        <v>3.5914</v>
       </c>
       <c r="Z10" t="n">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="AA10" t="n">
-        <v>594</v>
+        <v>657</v>
       </c>
       <c r="AB10" t="n">
-        <v>395.8183</v>
+        <v>424.0315</v>
       </c>
       <c r="AC10" t="n">
-        <v>926.7320999999999</v>
+        <v>972.2885</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>14</v>
@@ -3255,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.0175</v>
+        <v>7.2034</v>
       </c>
     </row>
     <row r="11">
@@ -3293,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="N11" t="n">
-        <v>756</v>
+        <v>817</v>
       </c>
       <c r="O11" t="n">
-        <v>1385.053</v>
+        <v>1505.2367</v>
       </c>
       <c r="P11" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.1331</v>
+        <v>23.1575</v>
       </c>
       <c r="R11" t="n">
         <v>245.9655</v>
@@ -3326,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.02950583</v>
+        <v>0.03352935</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03023879</v>
+        <v>0.03267869</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.4394</v>
+        <v>2.0328</v>
       </c>
       <c r="Z11" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="AA11" t="n">
-        <v>469</v>
+        <v>532</v>
       </c>
       <c r="AB11" t="n">
-        <v>328.7351</v>
+        <v>377.5341</v>
       </c>
       <c r="AC11" t="n">
-        <v>861.8082000000001</v>
+        <v>933.0214</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.6877</v>
+        <v>6.6802</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.875</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5632</v>
+        <v>3.7081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="D13" t="n">
-        <v>400.5</v>
+        <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>143.7856</v>
+        <v>190.5649</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1083.375</v>
+        <v>979.3333</v>
       </c>
       <c r="D14" t="n">
-        <v>939.5</v>
+        <v>918</v>
       </c>
       <c r="E14" t="n">
-        <v>361.3218</v>
+        <v>460.0611</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2933.1362</v>
+        <v>2613.486</v>
       </c>
       <c r="D15" t="n">
-        <v>1646.0321</v>
+        <v>1580.6387</v>
       </c>
       <c r="E15" t="n">
-        <v>2286.2961</v>
+        <v>2343.7881</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>138.125</v>
+        <v>123.2222</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>105.0842</v>
+        <v>107.987</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.3005</v>
+        <v>20.4972</v>
       </c>
       <c r="D17" t="n">
-        <v>21.6347</v>
+        <v>21.36</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7632</v>
+        <v>2.9202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>275.4257</v>
+        <v>253.4606</v>
       </c>
       <c r="D18" t="n">
-        <v>240.4299</v>
+        <v>234.8944</v>
       </c>
       <c r="E18" t="n">
-        <v>89.7432</v>
+        <v>106.7206</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10379.625</v>
+        <v>9783.3333</v>
       </c>
       <c r="D19" t="n">
-        <v>9533.5</v>
+        <v>9374</v>
       </c>
       <c r="E19" t="n">
-        <v>2334.0449</v>
+        <v>2822.5642</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24427.5</v>
+        <v>23226.1111</v>
       </c>
       <c r="D20" t="n">
-        <v>24429.5</v>
+        <v>23858</v>
       </c>
       <c r="E20" t="n">
-        <v>5136.867</v>
+        <v>6006.5793</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9949</v>
+        <v>0.9809</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0144</v>
+        <v>0.0441</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0440793</v>
+        <v>0.04040066</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04195089</v>
+        <v>0.0403243</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0069352</v>
+        <v>0.01280145</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04405889</v>
+        <v>0.04036312</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04366502</v>
+        <v>0.04105915</v>
       </c>
       <c r="E24" t="n">
-        <v>0.008148549999999999</v>
+        <v>0.01345466</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.2531</v>
+        <v>3.4633</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1586</v>
+        <v>3.2826</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9129</v>
+        <v>1.0616</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>397.75</v>
+        <v>359.1111</v>
       </c>
       <c r="D26" t="n">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="E26" t="n">
-        <v>138.6916</v>
+        <v>173.9759</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>902.875</v>
+        <v>808.1111</v>
       </c>
       <c r="D27" t="n">
-        <v>769</v>
+        <v>685</v>
       </c>
       <c r="E27" t="n">
-        <v>392.2617</v>
+        <v>464.1738</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>520.8569</v>
+        <v>469.7742</v>
       </c>
       <c r="D28" t="n">
-        <v>452.8123</v>
+        <v>440.2498</v>
       </c>
       <c r="E28" t="n">
-        <v>155.3532</v>
+        <v>211.1936</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1226.0753</v>
+        <v>1107.8014</v>
       </c>
       <c r="D29" t="n">
-        <v>1049.9026</v>
+        <v>1027.4529</v>
       </c>
       <c r="E29" t="n">
-        <v>394.1536</v>
+        <v>511.699</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.875</v>
+        <v>9.777799999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>3.9799</v>
+        <v>4.9694</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7033</v>
+        <v>5.6789</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.25</v>
+        <v>14.5556</v>
       </c>
       <c r="D32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>5.3117</v>
+        <v>7.1083</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.1884</v>
+        <v>6.9508</v>
       </c>
       <c r="D33" t="n">
-        <v>7.3449</v>
+        <v>7.2034</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4664</v>
+        <v>0.8357</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1017909</v>
+        <v>1017684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35082</v>
+        <v>35081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03446477</v>
+        <v>0.03447141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00077708</v>
+        <v>0.00077824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.819999999999999e-06</v>
+        <v>1.081e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125.7419</v>
+        <v>125.2893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03880481</v>
+        <v>0.03880816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03544169</v>
+        <v>0.03544909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03446477</v>
+        <v>0.03447141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03545798</v>
+        <v>0.03546484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.5376</v>
+        <v>7.5333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33419</v>
+        <v>33418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.8116</v>
+        <v>18.6454</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4438</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.7141</v>
+        <v>43.7029</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3826</v>
+        <v>0.3796</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6204</v>
       </c>
     </row>
     <row r="15">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2259,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3437,6 +3437,86 @@
       </c>
       <c r="AG11" t="n">
         <v>6.6802</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>347.0489</v>
+      </c>
+      <c r="J12" t="n">
+        <v>976.84</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>147</v>
+      </c>
+      <c r="O12" t="n">
+        <v>56.2843</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14.0711</v>
+      </c>
+      <c r="R12" t="n">
+        <v>77.7401</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5013</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13615</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8689</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01097147</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01079692</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.1453</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>61.1127</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>161.6102</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.05</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.333299999999999</v>
+        <v>10.6667</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7081</v>
+        <v>3.7749</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>415</v>
+        <v>415.1111</v>
       </c>
       <c r="D13" t="n">
         <v>400</v>
       </c>
       <c r="E13" t="n">
-        <v>190.5649</v>
+        <v>190.5331</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>979.3333</v>
+        <v>979.4444</v>
       </c>
       <c r="D14" t="n">
         <v>918</v>
       </c>
       <c r="E14" t="n">
-        <v>460.0611</v>
+        <v>460.0215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2613.486</v>
+        <v>2620.6445</v>
       </c>
       <c r="D15" t="n">
-        <v>1580.6387</v>
+        <v>1728.0824</v>
       </c>
       <c r="E15" t="n">
-        <v>2343.7881</v>
+        <v>2258.9938</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>123.2222</v>
+        <v>123.5556</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>107.987</v>
+        <v>104.53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.4972</v>
+        <v>20.5061</v>
       </c>
       <c r="D17" t="n">
-        <v>21.36</v>
+        <v>21.7618</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9202</v>
+        <v>2.836</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04040066</v>
+        <v>0.04041286</v>
       </c>
       <c r="D23" t="n">
         <v>0.0403243</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01280145</v>
+        <v>0.01280128</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04036312</v>
+        <v>0.04036778</v>
       </c>
       <c r="D24" t="n">
         <v>0.04105915</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01345466</v>
+        <v>0.01345254</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.4633</v>
+        <v>4.5208</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2826</v>
+        <v>4.2137</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0616</v>
+        <v>1.3425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>359.1111</v>
+        <v>359.2222</v>
       </c>
       <c r="D26" t="n">
         <v>322</v>
       </c>
       <c r="E26" t="n">
-        <v>173.9759</v>
+        <v>173.9337</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>808.1111</v>
+        <v>808.2222</v>
       </c>
       <c r="D27" t="n">
         <v>685</v>
       </c>
       <c r="E27" t="n">
-        <v>464.1738</v>
+        <v>464.1333</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>469.7742</v>
+        <v>469.9774</v>
       </c>
       <c r="D28" t="n">
         <v>440.2498</v>
       </c>
       <c r="E28" t="n">
-        <v>211.1936</v>
+        <v>211.145</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1107.8014</v>
+        <v>1108.0045</v>
       </c>
       <c r="D29" t="n">
         <v>1027.4529</v>
       </c>
       <c r="E29" t="n">
-        <v>511.699</v>
+        <v>511.6388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.9508</v>
+        <v>6.9608</v>
       </c>
       <c r="D33" t="n">
-        <v>7.2034</v>
+        <v>7.2936</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8357</v>
+        <v>0.8397</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35081</v>
+        <v>35082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03447141</v>
+        <v>0.03447239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125.2893</v>
+        <v>125.2929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03880816</v>
+        <v>0.03880996</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03544909</v>
+        <v>0.03545015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03447141</v>
+        <v>0.03447239</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03546484</v>
+        <v>0.03546582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.5333</v>
+        <v>7.5343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33418</v>
+        <v>33419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>403</v>
@@ -2473,13 +2473,13 @@
         <v>1050</v>
       </c>
       <c r="O2" t="n">
-        <v>4607.841</v>
+        <v>4660.8826</v>
       </c>
       <c r="P2" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.6916</v>
+        <v>19.6662</v>
       </c>
       <c r="R2" t="n">
         <v>769.5412</v>
@@ -2503,7 +2503,7 @@
         <v>0.03578244</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2995</v>
+        <v>1.4294</v>
       </c>
       <c r="Z2" t="n">
         <v>320</v>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>378</v>
@@ -2574,13 +2574,13 @@
         <v>961</v>
       </c>
       <c r="O3" t="n">
-        <v>1407.3595</v>
+        <v>1532.9575</v>
       </c>
       <c r="P3" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.5467</v>
+        <v>20.4394</v>
       </c>
       <c r="R3" t="n">
         <v>234.8944</v>
@@ -2604,7 +2604,7 @@
         <v>0.04627088</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5543</v>
+        <v>3.4058</v>
       </c>
       <c r="Z3" t="n">
         <v>322</v>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
         <v>453</v>
@@ -2675,13 +2675,13 @@
         <v>1087</v>
       </c>
       <c r="O4" t="n">
-        <v>3571.2258</v>
+        <v>2976.0105</v>
       </c>
       <c r="P4" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.9094</v>
+        <v>22.0445</v>
       </c>
       <c r="R4" t="n">
         <v>313.9483</v>
@@ -2705,7 +2705,7 @@
         <v>0.04105915</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1408</v>
+        <v>4.7779</v>
       </c>
       <c r="Z4" t="n">
         <v>434</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M5" t="n">
         <v>743</v>
@@ -2776,13 +2776,13 @@
         <v>1814</v>
       </c>
       <c r="O5" t="n">
-        <v>5105.9802</v>
+        <v>4995.4532</v>
       </c>
       <c r="P5" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.4144</v>
+        <v>19.1397</v>
       </c>
       <c r="R5" t="n">
         <v>456.9605</v>
@@ -2806,7 +2806,7 @@
         <v>0.05563564</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.2826</v>
+        <v>3.7202</v>
       </c>
       <c r="Z5" t="n">
         <v>671</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>401</v>
@@ -2877,13 +2877,13 @@
         <v>801</v>
       </c>
       <c r="O6" t="n">
-        <v>1580.6387</v>
+        <v>1588.6093</v>
       </c>
       <c r="P6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.36</v>
+        <v>21.7618</v>
       </c>
       <c r="R6" t="n">
         <v>233.2376</v>
@@ -2907,7 +2907,7 @@
         <v>0.04082361</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5725</v>
+        <v>4.7162</v>
       </c>
       <c r="Z6" t="n">
         <v>350</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -2978,13 +2978,13 @@
         <v>918</v>
       </c>
       <c r="O7" t="n">
-        <v>1711.4255</v>
+        <v>1728.0824</v>
       </c>
       <c r="P7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q7" t="n">
-        <v>19.0158</v>
+        <v>18.9899</v>
       </c>
       <c r="R7" t="n">
         <v>166.1249</v>
@@ -3008,7 +3008,7 @@
         <v>0.05268595</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.8157</v>
+        <v>4.2137</v>
       </c>
       <c r="Z7" t="n">
         <v>319</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
         <v>614</v>
@@ -3210,7 +3210,7 @@
         <v>0.04840232</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.0347</v>
+        <v>3.9451</v>
       </c>
       <c r="Z9" t="n">
         <v>525</v>
@@ -3272,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N10" t="n">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="O10" t="n">
-        <v>1122.857</v>
+        <v>1742.8002</v>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.3929</v>
+        <v>22.3436</v>
       </c>
       <c r="R10" t="n">
         <v>222.7523</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04020211</v>
+        <v>0.04031195</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03491491</v>
+        <v>0.03495683</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.5914</v>
+        <v>4.9382</v>
       </c>
       <c r="Z10" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA10" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AB10" t="n">
-        <v>424.0315</v>
+        <v>425.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>972.2885</v>
+        <v>974.1169</v>
       </c>
       <c r="AD10" t="n">
         <v>9</v>
@@ -3335,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.2034</v>
+        <v>7.2936</v>
       </c>
     </row>
     <row r="11">
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>325</v>
@@ -3412,7 +3412,7 @@
         <v>0.03267869</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.0328</v>
+        <v>3.2525</v>
       </c>
       <c r="Z11" t="n">
         <v>261</v>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
         <v>55</v>
@@ -3492,7 +3492,7 @@
         <v>0.01079692</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.1453</v>
+        <v>7.718</v>
       </c>
       <c r="Z12" t="n">
         <v>50</v>

--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.6667</v>
+        <v>12.5556</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7749</v>
+        <v>6.0023</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>415.1111</v>
+        <v>454.1111</v>
       </c>
       <c r="D13" t="n">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="E13" t="n">
-        <v>190.5331</v>
+        <v>220.2677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>979.4444</v>
+        <v>1028.1111</v>
       </c>
       <c r="D14" t="n">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="E14" t="n">
-        <v>460.0215</v>
+        <v>492.2495</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2620.6445</v>
+        <v>2820.835</v>
       </c>
       <c r="D15" t="n">
-        <v>1728.0824</v>
+        <v>1821.9525</v>
       </c>
       <c r="E15" t="n">
-        <v>2258.9938</v>
+        <v>2248.425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>123.5556</v>
+        <v>136.3333</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="E16" t="n">
-        <v>104.53</v>
+        <v>106.8936</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.5061</v>
+        <v>20.2611</v>
       </c>
       <c r="D17" t="n">
-        <v>21.7618</v>
+        <v>21.0348</v>
       </c>
       <c r="E17" t="n">
-        <v>2.836</v>
+        <v>2.6495</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04041286</v>
+        <v>0.04403147</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0403243</v>
+        <v>0.04444686</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01280128</v>
+        <v>0.01477043</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04036778</v>
+        <v>0.04241266</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04105915</v>
+        <v>0.04241898</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01345254</v>
+        <v>0.01489803</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.5208</v>
+        <v>5.0992</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2137</v>
+        <v>4.8144</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3425</v>
+        <v>1.4035</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>359.2222</v>
+        <v>408.1111</v>
       </c>
       <c r="D26" t="n">
-        <v>322</v>
+        <v>390</v>
       </c>
       <c r="E26" t="n">
-        <v>173.9337</v>
+        <v>212.8881</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>808.2222</v>
+        <v>873.5556</v>
       </c>
       <c r="D27" t="n">
-        <v>685</v>
+        <v>752</v>
       </c>
       <c r="E27" t="n">
-        <v>464.1333</v>
+        <v>503.4181</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>469.9774</v>
+        <v>513.9893</v>
       </c>
       <c r="D28" t="n">
-        <v>440.2498</v>
+        <v>487.9066</v>
       </c>
       <c r="E28" t="n">
-        <v>211.145</v>
+        <v>244.88</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1108.0045</v>
+        <v>1162.9909</v>
       </c>
       <c r="D29" t="n">
-        <v>1027.4529</v>
+        <v>1077.524</v>
       </c>
       <c r="E29" t="n">
-        <v>511.6388</v>
+        <v>548.1787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.777799999999999</v>
+        <v>10.6667</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>4.9694</v>
+        <v>6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>13.2222</v>
       </c>
       <c r="D31" t="n">
         <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6789</v>
+        <v>5.6298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.5556</v>
+        <v>14.8889</v>
       </c>
       <c r="D32" t="n">
         <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>7.1083</v>
+        <v>7.1492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.9608</v>
+        <v>6.8931</v>
       </c>
       <c r="D33" t="n">
-        <v>7.2936</v>
+        <v>7.2875</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8397</v>
+        <v>0.8108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35082</v>
+        <v>36616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03447239</v>
+        <v>0.03597973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>792</v>
+        <v>842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00077824</v>
+        <v>0.00082737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>125.2929</v>
+        <v>134.1245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03880996</v>
+        <v>0.04048176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03545015</v>
+        <v>0.0370742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03447239</v>
+        <v>0.03597973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03546582</v>
+        <v>0.03697317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.5343</v>
+        <v>7.5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33419</v>
+        <v>34950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>627</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.6454</v>
+        <v>18.3278</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4223</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.7029</v>
+        <v>43.7163</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3796</v>
+        <v>0.3695</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6204</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2473,13 +2473,13 @@
         <v>1050</v>
       </c>
       <c r="O2" t="n">
-        <v>4660.8826</v>
+        <v>4532.3557</v>
       </c>
       <c r="P2" t="n">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.6662</v>
+        <v>19.8788</v>
       </c>
       <c r="R2" t="n">
         <v>769.5412</v>
@@ -2565,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>378</v>
+        <v>458</v>
       </c>
       <c r="N3" t="n">
-        <v>961</v>
+        <v>1126</v>
       </c>
       <c r="O3" t="n">
-        <v>1532.9575</v>
+        <v>2957.8784</v>
       </c>
       <c r="P3" t="n">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.4394</v>
+        <v>19.3325</v>
       </c>
       <c r="R3" t="n">
         <v>234.8944</v>
@@ -2598,37 +2598,37 @@
         <v>0.9593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0403243</v>
+        <v>0.04885854</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04627088</v>
+        <v>0.05421542</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.4058</v>
+        <v>5.1087</v>
       </c>
       <c r="Z3" t="n">
-        <v>322</v>
+        <v>409</v>
       </c>
       <c r="AA3" t="n">
-        <v>853</v>
+        <v>1034</v>
       </c>
       <c r="AB3" t="n">
-        <v>425.8772</v>
+        <v>515.4041</v>
       </c>
       <c r="AC3" t="n">
-        <v>1072.3524</v>
+        <v>1258.2346</v>
       </c>
       <c r="AD3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.5912</v>
+        <v>7.5572</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M4" t="n">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="N4" t="n">
-        <v>1087</v>
+        <v>1123</v>
       </c>
       <c r="O4" t="n">
-        <v>2976.0105</v>
+        <v>3050.0521</v>
       </c>
       <c r="P4" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.0445</v>
+        <v>21.0348</v>
       </c>
       <c r="R4" t="n">
         <v>313.9483</v>
@@ -2699,28 +2699,28 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04018095</v>
+        <v>0.04337414</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04105915</v>
+        <v>0.04241898</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.7779</v>
+        <v>7.0075</v>
       </c>
       <c r="Z4" t="n">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="AA4" t="n">
-        <v>883</v>
+        <v>919</v>
       </c>
       <c r="AB4" t="n">
-        <v>519.1737000000001</v>
+        <v>557.4874</v>
       </c>
       <c r="AC4" t="n">
-        <v>1247.7149</v>
+        <v>1286.0286</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>13</v>
@@ -2729,7 +2729,7 @@
         <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.4864</v>
+        <v>7.361</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M5" t="n">
-        <v>743</v>
+        <v>861</v>
       </c>
       <c r="N5" t="n">
-        <v>1814</v>
+        <v>1932</v>
       </c>
       <c r="O5" t="n">
-        <v>4995.4532</v>
+        <v>5133.7791</v>
       </c>
       <c r="P5" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.1397</v>
+        <v>18.6683</v>
       </c>
       <c r="R5" t="n">
         <v>456.9605</v>
@@ -2800,28 +2800,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04958953</v>
+        <v>0.05746513</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05563564</v>
+        <v>0.05925472</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.7202</v>
+        <v>4.8144</v>
       </c>
       <c r="Z5" t="n">
-        <v>671</v>
+        <v>822</v>
       </c>
       <c r="AA5" t="n">
-        <v>1721</v>
+        <v>1848</v>
       </c>
       <c r="AB5" t="n">
-        <v>822.9138</v>
+        <v>958.5828</v>
       </c>
       <c r="AC5" t="n">
-        <v>2034.8347</v>
+        <v>2170.5038</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -2830,7 +2830,7 @@
         <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.6399</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="6">
@@ -2868,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N6" t="n">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="O6" t="n">
-        <v>1588.6093</v>
+        <v>1592.6093</v>
       </c>
       <c r="P6" t="n">
         <v>73</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.7618</v>
+        <v>21.8166</v>
       </c>
       <c r="R6" t="n">
         <v>233.2376</v>
@@ -2901,25 +2901,25 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04357748</v>
+        <v>0.04444686</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04082361</v>
+        <v>0.04123133</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.7162</v>
+        <v>4.2875</v>
       </c>
       <c r="Z6" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AA6" t="n">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="AB6" t="n">
-        <v>465.3747</v>
+        <v>475.6173</v>
       </c>
       <c r="AC6" t="n">
-        <v>930.9209</v>
+        <v>941.1636</v>
       </c>
       <c r="AD6" t="n">
         <v>6</v>
@@ -2931,7 +2931,7 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.8902</v>
+        <v>6.856</v>
       </c>
     </row>
     <row r="7">
@@ -2972,19 +2972,19 @@
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="N7" t="n">
-        <v>918</v>
+        <v>965</v>
       </c>
       <c r="O7" t="n">
-        <v>1728.0824</v>
+        <v>1821.9525</v>
       </c>
       <c r="P7" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.9899</v>
+        <v>18.783</v>
       </c>
       <c r="R7" t="n">
         <v>166.1249</v>
@@ -3002,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05414918</v>
+        <v>0.06024096</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05268595</v>
+        <v>0.05538338</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2137</v>
       </c>
       <c r="Z7" t="n">
-        <v>319</v>
+        <v>390</v>
       </c>
       <c r="AA7" t="n">
-        <v>667</v>
+        <v>752</v>
       </c>
       <c r="AB7" t="n">
-        <v>440.2498</v>
+        <v>487.9066</v>
       </c>
       <c r="AC7" t="n">
-        <v>1027.4529</v>
+        <v>1077.524</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -3032,7 +3032,7 @@
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.4357</v>
+        <v>6.3276</v>
       </c>
     </row>
     <row r="8">
@@ -3073,19 +3073,19 @@
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="N8" t="n">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="O8" t="n">
-        <v>405.0437</v>
+        <v>410.4579</v>
       </c>
       <c r="P8" t="n">
         <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.7536</v>
+        <v>34.2048</v>
       </c>
       <c r="R8" t="n">
         <v>122.6041</v>
@@ -3103,28 +3103,28 @@
         <v>0.5802</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03676283</v>
+        <v>0.04237937</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03796034</v>
+        <v>0.04003777</v>
       </c>
       <c r="Y8" t="n">
         <v>2.4469</v>
       </c>
       <c r="Z8" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="AA8" t="n">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="AB8" t="n">
-        <v>170.1665</v>
+        <v>194.8234</v>
       </c>
       <c r="AC8" t="n">
-        <v>477.4285</v>
+        <v>502.0854</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.0372</v>
+        <v>5.7406</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="N9" t="n">
-        <v>1436</v>
+        <v>1479</v>
       </c>
       <c r="O9" t="n">
-        <v>7460.3662</v>
+        <v>7513.3367</v>
       </c>
       <c r="P9" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.6072</v>
+        <v>22.2948</v>
       </c>
       <c r="R9" t="n">
         <v>329.5219</v>
@@ -3204,28 +3204,28 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05108153</v>
+        <v>0.0546589</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04840232</v>
+        <v>0.04985169</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.9451</v>
+        <v>4.5521</v>
       </c>
       <c r="Z9" t="n">
-        <v>525</v>
+        <v>585</v>
       </c>
       <c r="AA9" t="n">
-        <v>1225</v>
+        <v>1319</v>
       </c>
       <c r="AB9" t="n">
-        <v>691.7006</v>
+        <v>744.5706</v>
       </c>
       <c r="AC9" t="n">
-        <v>1590.0164</v>
+        <v>1642.8864</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -3234,7 +3234,7 @@
         <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.5804</v>
+        <v>7.4593</v>
       </c>
     </row>
     <row r="10">
@@ -3275,19 +3275,19 @@
         <v>11</v>
       </c>
       <c r="M10" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="N10" t="n">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="O10" t="n">
-        <v>1742.8002</v>
+        <v>1752.386</v>
       </c>
       <c r="P10" t="n">
         <v>78</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.3436</v>
+        <v>22.4665</v>
       </c>
       <c r="R10" t="n">
         <v>222.7523</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04031195</v>
+        <v>0.04141037</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03495683</v>
+        <v>0.03537597</v>
       </c>
       <c r="Y10" t="n">
         <v>4.9382</v>
       </c>
       <c r="Z10" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AA10" t="n">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AB10" t="n">
-        <v>425.86</v>
+        <v>435.4457</v>
       </c>
       <c r="AC10" t="n">
-        <v>974.1169</v>
+        <v>983.7027</v>
       </c>
       <c r="AD10" t="n">
         <v>9</v>
@@ -3335,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.2936</v>
+        <v>7.2875</v>
       </c>
     </row>
     <row r="11">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="N11" t="n">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="O11" t="n">
-        <v>1505.2367</v>
+        <v>1506.4083</v>
       </c>
       <c r="P11" t="n">
         <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.1575</v>
+        <v>23.1755</v>
       </c>
       <c r="R11" t="n">
         <v>245.9655</v>
@@ -3406,28 +3406,28 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03352935</v>
+        <v>0.03445786</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03267869</v>
+        <v>0.03303868</v>
       </c>
       <c r="Y11" t="n">
         <v>3.2525</v>
       </c>
       <c r="Z11" t="n">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="AA11" t="n">
-        <v>532</v>
+        <v>582</v>
       </c>
       <c r="AB11" t="n">
-        <v>377.5341</v>
+        <v>386.9483</v>
       </c>
       <c r="AC11" t="n">
-        <v>933.0214</v>
+        <v>942.4356</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
@@ -3436,7 +3436,7 @@
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.6802</v>
+        <v>6.8024</v>
       </c>
     </row>
     <row r="12">
@@ -3456,19 +3456,19 @@
         <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12" t="n">
-        <v>56.2843</v>
+        <v>59.1127</v>
       </c>
       <c r="P12" t="n">
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.0711</v>
+        <v>14.7782</v>
       </c>
       <c r="R12" t="n">
         <v>77.7401</v>
@@ -3486,25 +3486,25 @@
         <v>0.8689</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01097147</v>
+        <v>0.01137044</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01079692</v>
+        <v>0.01094381</v>
       </c>
       <c r="Y12" t="n">
         <v>7.718</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AA12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AB12" t="n">
-        <v>61.1127</v>
+        <v>63.9411</v>
       </c>
       <c r="AC12" t="n">
-        <v>161.6102</v>
+        <v>164.4386</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -3516,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.05</v>
+        <v>5.0071</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12.5556</v>
+        <v>12.3333</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0023</v>
+        <v>4.3589</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>454.1111</v>
+        <v>463.1111</v>
       </c>
       <c r="D13" t="n">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="E13" t="n">
-        <v>220.2677</v>
+        <v>206.7084</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1028.1111</v>
+        <v>1040.4444</v>
       </c>
       <c r="D14" t="n">
-        <v>965</v>
+        <v>1006</v>
       </c>
       <c r="E14" t="n">
-        <v>492.2495</v>
+        <v>482.8698</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2820.835</v>
+        <v>2873.3328</v>
       </c>
       <c r="D15" t="n">
-        <v>1821.9525</v>
+        <v>2003.7342</v>
       </c>
       <c r="E15" t="n">
-        <v>2248.425</v>
+        <v>2254.7723</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>136.3333</v>
+        <v>141.7778</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E16" t="n">
-        <v>106.8936</v>
+        <v>107.352</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.2611</v>
+        <v>19.2389</v>
       </c>
       <c r="D17" t="n">
-        <v>21.0348</v>
+        <v>19.6911</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6495</v>
+        <v>4.2714</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04403147</v>
+        <v>0.04539679</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04444686</v>
+        <v>0.04759835</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01477043</v>
+        <v>0.0143176</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04241266</v>
+        <v>0.0431795</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04241898</v>
+        <v>0.04287225</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01489803</v>
+        <v>0.01518492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.0992</v>
+        <v>5.1608</v>
       </c>
       <c r="D25" t="n">
-        <v>4.8144</v>
+        <v>5.3871</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4035</v>
+        <v>1.1999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>408.1111</v>
+        <v>423.8889</v>
       </c>
       <c r="D26" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="E26" t="n">
-        <v>212.8881</v>
+        <v>203.9886</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>873.5556</v>
+        <v>899.4444</v>
       </c>
       <c r="D27" t="n">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="E27" t="n">
-        <v>503.4181</v>
+        <v>505.7383</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>513.9893</v>
+        <v>524.8605</v>
       </c>
       <c r="D28" t="n">
-        <v>487.9066</v>
+        <v>517.6051</v>
       </c>
       <c r="E28" t="n">
-        <v>244.88</v>
+        <v>231.013</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1162.9909</v>
+        <v>1178.3413</v>
       </c>
       <c r="D29" t="n">
-        <v>1077.524</v>
+        <v>1133.7077</v>
       </c>
       <c r="E29" t="n">
-        <v>548.1787</v>
+        <v>538.7522</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10.6667</v>
+        <v>11.1111</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>5.4416</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.2222</v>
+        <v>13.5556</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6298</v>
+        <v>5.615</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.8889</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>7.1492</v>
+        <v>7.1239</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>14.2222</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12.235</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>6.8931</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.2875</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.8108</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.1358</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.3348</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6168</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36616</v>
+        <v>36997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03597973</v>
+        <v>0.03635411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>842</v>
+        <v>873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00082737</v>
+        <v>0.00085783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>134.1245</v>
+        <v>140.1402</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04048176</v>
+        <v>0.04091913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0370742</v>
+        <v>0.03741577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03597973</v>
+        <v>0.03635411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03697317</v>
+        <v>0.03734755</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>181</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.5197</v>
+        <v>7.5429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1806,7 +1924,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.1782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34950</v>
+        <v>35272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.3278</v>
+        <v>18.9739</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43.7163</v>
+        <v>43.9374</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0471</v>
+        <v>50.0493</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3695</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6117</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -2245,7 +2363,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.3232</v>
       </c>
     </row>
   </sheetData>
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>403</v>
+        <v>461</v>
       </c>
       <c r="N2" t="n">
-        <v>1050</v>
+        <v>1108</v>
       </c>
       <c r="O2" t="n">
-        <v>4532.3557</v>
+        <v>4592.2258</v>
       </c>
       <c r="P2" t="n">
         <v>228</v>
       </c>
       <c r="Q2" t="n">
-        <v>19.8788</v>
+        <v>20.1413</v>
       </c>
       <c r="R2" t="n">
         <v>769.5412</v>
@@ -2497,37 +2625,43 @@
         <v>0.6229</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02805039</v>
+        <v>0.03208742</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03578244</v>
+        <v>0.037759</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4294</v>
+        <v>2.0792</v>
       </c>
       <c r="Z2" t="n">
-        <v>320</v>
+        <v>408</v>
       </c>
       <c r="AA2" t="n">
-        <v>687</v>
+        <v>759</v>
       </c>
       <c r="AB2" t="n">
-        <v>444.3625</v>
+        <v>515.5462</v>
       </c>
       <c r="AC2" t="n">
-        <v>1138.6833</v>
+        <v>1209.8671</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.308</v>
+        <v>6.2155</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.2412</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2699,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>458</v>
+        <v>507</v>
       </c>
       <c r="N3" t="n">
-        <v>1126</v>
+        <v>1199</v>
       </c>
       <c r="O3" t="n">
-        <v>2957.8784</v>
+        <v>3217.7312</v>
       </c>
       <c r="P3" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="Q3" t="n">
-        <v>19.3325</v>
+        <v>18.9278</v>
       </c>
       <c r="R3" t="n">
         <v>234.8944</v>
@@ -2598,37 +2732,43 @@
         <v>0.9593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04885854</v>
+        <v>0.05408577</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05421542</v>
+        <v>0.05773027</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.1087</v>
+        <v>5.5344</v>
       </c>
       <c r="Z3" t="n">
-        <v>409</v>
+        <v>492</v>
       </c>
       <c r="AA3" t="n">
-        <v>1034</v>
+        <v>1165</v>
       </c>
       <c r="AB3" t="n">
-        <v>515.4041</v>
+        <v>574.4457</v>
       </c>
       <c r="AC3" t="n">
-        <v>1258.2346</v>
+        <v>1346.4184</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.5572</v>
+        <v>7.8188</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.4235</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="N4" t="n">
-        <v>1123</v>
+        <v>1135</v>
       </c>
       <c r="O4" t="n">
-        <v>3050.0521</v>
+        <v>3032.4247</v>
       </c>
       <c r="P4" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.0348</v>
+        <v>19.6911</v>
       </c>
       <c r="R4" t="n">
         <v>313.9483</v>
@@ -2699,37 +2839,43 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04337414</v>
+        <v>0.04408373</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04241898</v>
+        <v>0.04287225</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.0075</v>
+        <v>5.7334</v>
       </c>
       <c r="Z4" t="n">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AA4" t="n">
-        <v>919</v>
+        <v>979</v>
       </c>
       <c r="AB4" t="n">
-        <v>557.4874</v>
+        <v>567.6589</v>
       </c>
       <c r="AC4" t="n">
-        <v>1286.0286</v>
+        <v>1300.7859</v>
       </c>
       <c r="AD4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE4" t="n">
         <v>14</v>
       </c>
-      <c r="AE4" t="n">
-        <v>13</v>
-      </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.361</v>
+        <v>7.4165</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2532</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
-        <v>861</v>
+        <v>820</v>
       </c>
       <c r="N5" t="n">
-        <v>1932</v>
+        <v>1896</v>
       </c>
       <c r="O5" t="n">
-        <v>5133.7791</v>
+        <v>5066.0807</v>
       </c>
       <c r="P5" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.6683</v>
+        <v>18.9033</v>
       </c>
       <c r="R5" t="n">
         <v>456.9605</v>
@@ -2800,28 +2946,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05746513</v>
+        <v>0.05472869</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05925472</v>
+        <v>0.05815059</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.8144</v>
+        <v>4.1579</v>
       </c>
       <c r="Z5" t="n">
-        <v>822</v>
+        <v>794</v>
       </c>
       <c r="AA5" t="n">
-        <v>1848</v>
+        <v>1835</v>
       </c>
       <c r="AB5" t="n">
-        <v>958.5828</v>
+        <v>915.0975</v>
       </c>
       <c r="AC5" t="n">
-        <v>2170.5038</v>
+        <v>2133.4327</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -2830,7 +2976,13 @@
         <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.38</v>
+        <v>7.4488</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4739</v>
       </c>
     </row>
     <row r="6">
@@ -2871,19 +3023,19 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="N6" t="n">
-        <v>809</v>
+        <v>838</v>
       </c>
       <c r="O6" t="n">
-        <v>1592.6093</v>
+        <v>1629.9525</v>
       </c>
       <c r="P6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.8166</v>
+        <v>21.7327</v>
       </c>
       <c r="R6" t="n">
         <v>233.2376</v>
@@ -2901,28 +3053,28 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04444686</v>
+        <v>0.04759835</v>
       </c>
       <c r="X6" t="n">
-        <v>0.04123133</v>
+        <v>0.04270934</v>
       </c>
       <c r="Y6" t="n">
         <v>4.2875</v>
       </c>
       <c r="Z6" t="n">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="AA6" t="n">
-        <v>693</v>
+        <v>722</v>
       </c>
       <c r="AB6" t="n">
-        <v>475.6173</v>
+        <v>501.3747</v>
       </c>
       <c r="AC6" t="n">
-        <v>941.1636</v>
+        <v>966.9209</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -2931,7 +3083,13 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.856</v>
+        <v>7.1556</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3333</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +3127,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="N7" t="n">
-        <v>965</v>
+        <v>1006</v>
       </c>
       <c r="O7" t="n">
-        <v>1821.9525</v>
+        <v>2003.7342</v>
       </c>
       <c r="P7" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.783</v>
+        <v>18.2158</v>
       </c>
       <c r="R7" t="n">
         <v>166.1249</v>
@@ -3002,37 +3160,43 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06024096</v>
+        <v>0.06294842</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05538338</v>
+        <v>0.05773646</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2137</v>
+        <v>5.4176</v>
       </c>
       <c r="Z7" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="AA7" t="n">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="AB7" t="n">
-        <v>487.9066</v>
+        <v>517.6051</v>
       </c>
       <c r="AC7" t="n">
-        <v>1077.524</v>
+        <v>1133.7077</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
         <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.3276</v>
+        <v>6.4611</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4364</v>
       </c>
     </row>
     <row r="8">
@@ -3070,22 +3234,22 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N8" t="n">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="O8" t="n">
-        <v>410.4579</v>
+        <v>425.3574</v>
       </c>
       <c r="P8" t="n">
         <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.2048</v>
+        <v>35.4465</v>
       </c>
       <c r="R8" t="n">
         <v>122.6041</v>
@@ -3103,28 +3267,28 @@
         <v>0.5802</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04237937</v>
+        <v>0.04493235</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04003777</v>
+        <v>0.04117092</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.4469</v>
+        <v>3.2625</v>
       </c>
       <c r="Z8" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AA8" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AB8" t="n">
-        <v>194.8234</v>
+        <v>205.8944</v>
       </c>
       <c r="AC8" t="n">
-        <v>502.0854</v>
+        <v>515.5706</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -3133,7 +3297,13 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.7406</v>
+        <v>5.5304</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3174,19 +3344,19 @@
         <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="N9" t="n">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="O9" t="n">
-        <v>7513.3367</v>
+        <v>7603.1357</v>
       </c>
       <c r="P9" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.2948</v>
+        <v>21.9111</v>
       </c>
       <c r="R9" t="n">
         <v>329.5219</v>
@@ -3204,25 +3374,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0546589</v>
+        <v>0.05415973</v>
       </c>
       <c r="X9" t="n">
-        <v>0.04985169</v>
+        <v>0.0499191</v>
       </c>
       <c r="Y9" t="n">
         <v>4.5521</v>
       </c>
       <c r="Z9" t="n">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="AA9" t="n">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="AB9" t="n">
-        <v>744.5706</v>
+        <v>738.5706</v>
       </c>
       <c r="AC9" t="n">
-        <v>1642.8864</v>
+        <v>1645.3006</v>
       </c>
       <c r="AD9" t="n">
         <v>15</v>
@@ -3234,7 +3404,13 @@
         <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4593</v>
+        <v>7.4475</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4063</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N10" t="n">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="O10" t="n">
-        <v>1752.386</v>
+        <v>1758.0429</v>
       </c>
       <c r="P10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.4665</v>
+        <v>22.2537</v>
       </c>
       <c r="R10" t="n">
         <v>222.7523</v>
@@ -3305,25 +3481,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04141037</v>
+        <v>0.04163005</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03537597</v>
+        <v>0.0354598</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9382</v>
+        <v>5.3871</v>
       </c>
       <c r="Z10" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AA10" t="n">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AB10" t="n">
-        <v>435.4457</v>
+        <v>437.4457</v>
       </c>
       <c r="AC10" t="n">
-        <v>983.7027</v>
+        <v>985.7027</v>
       </c>
       <c r="AD10" t="n">
         <v>9</v>
@@ -3335,7 +3511,13 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.2875</v>
+        <v>7.3348</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2025</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="N11" t="n">
-        <v>826</v>
+        <v>798</v>
       </c>
       <c r="O11" t="n">
-        <v>1506.4083</v>
+        <v>1478.7809</v>
       </c>
       <c r="P11" t="n">
         <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>23.1755</v>
+        <v>22.7505</v>
       </c>
       <c r="R11" t="n">
         <v>245.9655</v>
@@ -3406,25 +3588,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03445786</v>
+        <v>0.03497369</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03303868</v>
+        <v>0.03191872</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.2525</v>
+        <v>3.659</v>
       </c>
       <c r="Z11" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AA11" t="n">
-        <v>582</v>
+        <v>553</v>
       </c>
       <c r="AB11" t="n">
-        <v>386.9483</v>
+        <v>392.7767</v>
       </c>
       <c r="AC11" t="n">
-        <v>942.4356</v>
+        <v>911.1219</v>
       </c>
       <c r="AD11" t="n">
         <v>8</v>
@@ -3436,7 +3618,13 @@
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.8024</v>
+        <v>7.333</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.4462</v>
       </c>
     </row>
     <row r="12">
@@ -3456,19 +3644,19 @@
         <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N12" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="O12" t="n">
-        <v>59.1127</v>
+        <v>70.1127</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.7782</v>
+        <v>8.764099999999999</v>
       </c>
       <c r="R12" t="n">
         <v>77.7401</v>
@@ -3486,28 +3674,28 @@
         <v>0.8689</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01137044</v>
+        <v>0.01436266</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01094381</v>
+        <v>0.01211899</v>
       </c>
       <c r="Y12" t="n">
         <v>7.718</v>
       </c>
       <c r="Z12" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="AA12" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="AB12" t="n">
-        <v>63.9411</v>
+        <v>78.7696</v>
       </c>
       <c r="AC12" t="n">
-        <v>164.4386</v>
+        <v>181.6812</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -3516,7 +3704,13 @@
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.0071</v>
+        <v>5.8058</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
